--- a/Ansible/audit_reports/report.xlsx
+++ b/Ansible/audit_reports/report.xlsx
@@ -537,19 +537,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>132</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5">
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U-02</t>
+          <t>U-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,9 +719,9 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U-03</t>
+          <t>U-02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U-04</t>
+          <t>U-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -789,9 +789,9 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U-05</t>
+          <t>U-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U-06</t>
+          <t>U-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U-07</t>
+          <t>U-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -894,9 +894,9 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U-08</t>
+          <t>U-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -929,9 +929,9 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -956,7 +956,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U-09</t>
+          <t>U-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U-10</t>
+          <t>U-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -999,9 +999,9 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U-11</t>
+          <t>U-06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1034,9 +1034,9 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U-12</t>
+          <t>U-06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U-13</t>
+          <t>U-07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1104,9 +1104,9 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1131,17 +1131,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U-14</t>
+          <t>U-07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1166,17 +1166,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U-15</t>
+          <t>U-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1201,17 +1201,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U-16</t>
+          <t>U-08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1236,17 +1236,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U-17</t>
+          <t>U-09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U-18</t>
+          <t>U-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1306,17 +1306,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U-19</t>
+          <t>U-10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1341,17 +1341,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U-20</t>
+          <t>U-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1376,17 +1376,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U-21</t>
+          <t>U-11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U-22</t>
+          <t>U-11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U-23</t>
+          <t>U-12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U-24</t>
+          <t>U-12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U-25</t>
+          <t>U-13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U-26</t>
+          <t>U-13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U-27</t>
+          <t>U-14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1594,9 +1594,9 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U-28</t>
+          <t>U-14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U-29</t>
+          <t>U-15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U-31</t>
+          <t>U-15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1699,9 +1699,9 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U-32</t>
+          <t>U-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U-33</t>
+          <t>U-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U-34</t>
+          <t>U-17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U-35</t>
+          <t>U-17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U-36</t>
+          <t>U-18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U-37</t>
+          <t>U-18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U-38</t>
+          <t>U-19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U-39</t>
+          <t>U-19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U-40</t>
+          <t>U-20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U-41</t>
+          <t>U-20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U-42</t>
+          <t>U-21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2111,17 +2111,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U-43</t>
+          <t>U-21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2146,17 +2146,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U-44</t>
+          <t>U-22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U-45</t>
+          <t>U-22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2216,17 +2216,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U-46</t>
+          <t>U-23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2251,17 +2251,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U-47</t>
+          <t>U-23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2286,17 +2286,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U-48</t>
+          <t>U-24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2321,17 +2321,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U-49</t>
+          <t>U-24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2356,17 +2356,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U-50</t>
+          <t>U-25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2391,17 +2391,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U-51</t>
+          <t>U-25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U-52</t>
+          <t>U-26</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2461,17 +2461,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U-53</t>
+          <t>U-26</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2496,17 +2496,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U-54</t>
+          <t>U-27</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2531,17 +2531,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U-55</t>
+          <t>U-27</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2566,17 +2566,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U-56</t>
+          <t>U-28</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U-57</t>
+          <t>U-28</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U-58</t>
+          <t>U-29</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>U-59</t>
+          <t>U-29</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2706,17 +2706,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U-60</t>
+          <t>U-30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2741,17 +2741,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U-61</t>
+          <t>U-31</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U-62</t>
+          <t>U-31</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2811,17 +2811,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>U-63</t>
+          <t>U-32</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U-64</t>
+          <t>U-32</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>패치 관리</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2881,17 +2881,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U-65</t>
+          <t>U-33</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>로그 관리</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2916,17 +2916,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U-66</t>
+          <t>U-33</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>로그 관리</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2951,17 +2951,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U-67</t>
+          <t>U-34</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>로그 관리</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2981,17 +2981,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U-01</t>
+          <t>U-34</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>계정 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3016,17 +3016,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U-02</t>
+          <t>U-35</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>계정 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3051,34 +3051,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U-03</t>
+          <t>U-35</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>계정 관리</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3086,17 +3086,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U-04</t>
+          <t>U-36</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>계정 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -3108,12 +3108,12 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3121,34 +3121,34 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>U-05</t>
+          <t>U-36</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>계정 관리</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3156,17 +3156,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U-06</t>
+          <t>U-37</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>계정 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3178,12 +3178,12 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -3191,34 +3191,34 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U-07</t>
+          <t>U-37</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>계정 관리</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3226,34 +3226,34 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U-08</t>
+          <t>U-38</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>계정 관리</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -3261,34 +3261,34 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>U-09</t>
+          <t>U-38</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>계정 관리</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -3296,17 +3296,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>U-10</t>
+          <t>U-39</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>계정 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -3318,12 +3318,12 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3331,34 +3331,34 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>U-11</t>
+          <t>U-39</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>계정 관리</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3366,34 +3366,34 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>U-12</t>
+          <t>U-40</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>계정 관리</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3401,17 +3401,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U-13</t>
+          <t>U-40</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>계정 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3436,17 +3436,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U-14</t>
+          <t>U-41</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3458,12 +3458,12 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3471,34 +3471,34 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U-15</t>
+          <t>U-41</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -3506,17 +3506,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>U-16</t>
+          <t>U-42</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -3528,12 +3528,12 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3541,17 +3541,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U-17</t>
+          <t>U-42</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -3563,12 +3563,12 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -3576,34 +3576,34 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>U-18</t>
+          <t>U-43</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -3611,17 +3611,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>U-19</t>
+          <t>U-43</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -3633,12 +3633,12 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -3646,17 +3646,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>U-20</t>
+          <t>U-44</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -3668,12 +3668,12 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -3681,17 +3681,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U-21</t>
+          <t>U-44</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -3716,17 +3716,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U-22</t>
+          <t>U-45</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -3738,12 +3738,12 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -3751,34 +3751,34 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U-23</t>
+          <t>U-45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -3786,17 +3786,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U-24</t>
+          <t>U-46</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -3808,12 +3808,12 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -3821,34 +3821,34 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U-25</t>
+          <t>U-46</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -3856,17 +3856,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U-26</t>
+          <t>U-47</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3878,12 +3878,12 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -3891,17 +3891,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U-27</t>
+          <t>U-47</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -3913,12 +3913,12 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -3926,34 +3926,34 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>U-28</t>
+          <t>U-48</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -3961,34 +3961,34 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>U-29</t>
+          <t>U-48</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -3996,34 +3996,34 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U-31</t>
+          <t>U-49</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -4031,34 +4031,34 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U-32</t>
+          <t>U-49</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4066,34 +4066,34 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>U-33</t>
+          <t>U-50</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>파일 및 디렉터리 관리</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -4101,12 +4101,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U-34</t>
+          <t>U-50</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4114,21 +4114,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -4136,12 +4136,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U-35</t>
+          <t>U-51</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4149,21 +4149,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -4171,12 +4171,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U-36</t>
+          <t>U-51</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4184,21 +4184,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -4206,12 +4206,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-37</t>
+          <t>U-52</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4228,12 +4228,12 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -4241,12 +4241,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-38</t>
+          <t>U-52</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4263,12 +4263,12 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -4276,12 +4276,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U-39</t>
+          <t>U-53</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4289,21 +4289,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -4311,12 +4311,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-40</t>
+          <t>U-53</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4324,21 +4324,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -4346,12 +4346,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-41</t>
+          <t>U-54</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4359,21 +4359,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -4381,12 +4381,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U-42</t>
+          <t>U-54</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4394,21 +4394,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -4416,12 +4416,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-43</t>
+          <t>U-55</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4438,12 +4438,12 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -4451,12 +4451,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-44</t>
+          <t>U-55</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4464,21 +4464,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -4486,12 +4486,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U-45</t>
+          <t>U-56</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4499,21 +4499,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -4521,12 +4521,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U-46</t>
+          <t>U-56</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4534,21 +4534,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -4556,12 +4556,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>U-47</t>
+          <t>U-57</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4578,12 +4578,12 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -4591,12 +4591,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U-48</t>
+          <t>U-57</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4604,21 +4604,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -4626,12 +4626,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>U-49</t>
+          <t>U-58</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4639,21 +4639,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -4661,12 +4661,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U-50</t>
+          <t>U-58</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4674,21 +4674,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -4696,12 +4696,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U-51</t>
+          <t>U-59</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4718,12 +4718,12 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -4731,12 +4731,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>U-52</t>
+          <t>U-59</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4744,21 +4744,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -4766,12 +4766,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>U-53</t>
+          <t>U-60</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4779,21 +4779,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -4801,12 +4801,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>U-54</t>
+          <t>U-60</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4814,21 +4814,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -4836,12 +4836,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>U-55</t>
+          <t>U-61</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4849,21 +4849,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -4871,12 +4871,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U-56</t>
+          <t>U-61</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4884,21 +4884,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -4906,12 +4906,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>U-57</t>
+          <t>U-62</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4928,12 +4928,12 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -4941,12 +4941,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>U-58</t>
+          <t>U-62</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4954,21 +4954,21 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -4976,12 +4976,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>U-59</t>
+          <t>U-63</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4998,12 +4998,12 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -5011,12 +5011,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>U-60</t>
+          <t>U-63</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5033,12 +5033,12 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -5046,17 +5046,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>U-61</t>
+          <t>U-64</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>패치 관리</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -5068,12 +5068,12 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -5081,34 +5081,34 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>U-62</t>
+          <t>U-64</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>VULNERABLE</t>
+          <t>패치 관리</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -5116,17 +5116,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>U-63</t>
+          <t>U-65</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>로그 관리</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -5138,12 +5138,12 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -5151,34 +5151,34 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>U-64</t>
+          <t>U-65</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>패치 관리</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+          <t>로그 관리</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -5186,12 +5186,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>U-65</t>
+          <t>U-66</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5199,21 +5199,21 @@
           <t>로그 관리</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5234,21 +5234,21 @@
           <t>로그 관리</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Rocky 9.5</t>
+          <t>Rocky 9.8</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5269,24 +5269,2369 @@
           <t>로그 관리</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
+          <t>Rocky 9.8</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>rocky1</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>U-67</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>로그 관리</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Rocky 9.8</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>5.14.0-687.39.1.el9_8.x86_64</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>U-01</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
           <t>Rocky 9.5</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>5.14.0-503.14.1.el9_5.x86_64</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>U-02</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>U-03</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>U-04</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>U-05</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>U-06</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>U-07</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>U-08</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>U-09</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>U-10</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>U-11</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>U-12</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>U-13</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>계정 관리</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>U-14</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>U-15</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>U-16</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>U-17</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>U-18</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>U-19</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>U-20</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>U-21</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>U-22</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>U-23</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>U-24</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>U-25</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>U-26</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>U-27</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>U-28</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>U-29</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>U-31</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>U-32</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>U-33</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>파일 및 디렉터리 관리</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>U-34</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>U-35</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>U-36</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>U-37</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>U-38</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>U-39</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>U-40</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>U-41</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>U-42</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>U-43</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>U-44</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>U-45</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>U-46</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>U-47</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>U-48</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>U-49</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>U-50</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>U-51</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>U-52</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>U-53</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>U-54</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>U-55</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>U-56</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>U-57</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>U-58</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>U-59</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>U-60</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>U-61</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>U-62</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>VULNERABLE</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>U-63</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>U-64</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>패치 관리</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>U-65</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>로그 관리</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>U-66</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>로그 관리</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>U-67</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>로그 관리</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Rocky 9.5</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>5.14.0-503.14.1.el9_5.x86_64</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5299,7 +7644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5363,7 +7708,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U-08</t>
+          <t>U-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5382,7 +7727,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U-11</t>
+          <t>U-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5401,12 +7746,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U-54</t>
+          <t>U-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5420,12 +7765,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U-56</t>
+          <t>U-11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -5439,12 +7784,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U-63</t>
+          <t>U-11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -5458,12 +7803,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U-64</t>
+          <t>U-54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>패치 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -5477,12 +7822,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U-65</t>
+          <t>U-54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>로그 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -5491,17 +7836,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U-07</t>
+          <t>U-56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>계정 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -5510,17 +7855,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U-08</t>
+          <t>U-56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>계정 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -5529,17 +7874,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U-11</t>
+          <t>U-63</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>계정 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -5548,12 +7893,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U-54</t>
+          <t>U-63</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5567,17 +7912,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U-56</t>
+          <t>U-64</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>패치 관리</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -5586,17 +7931,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rocky2</t>
+          <t>rocky1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U-58</t>
+          <t>U-65</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>로그 관리</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -5610,12 +7955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U-59</t>
+          <t>U-07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -5629,12 +7974,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U-60</t>
+          <t>U-08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -5648,12 +7993,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U-61</t>
+          <t>U-11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -5667,7 +8012,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U-63</t>
+          <t>U-54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5686,12 +8031,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U-64</t>
+          <t>U-56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>패치 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -5705,12 +8050,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U-65</t>
+          <t>U-58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>로그 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -5724,12 +8069,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U-66</t>
+          <t>U-59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>로그 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -5743,16 +8088,130 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U-67</t>
+          <t>U-60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>로그 관리</t>
+          <t>서비스 관리</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>U-61</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>U-63</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>U-64</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>패치 관리</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>U-65</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>로그 관리</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>U-66</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>로그 관리</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>rocky2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>U-67</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>로그 관리</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Ansible/audit_reports/report.xlsx
+++ b/Ansible/audit_reports/report.xlsx
@@ -36,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,13 +76,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,10 +531,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -547,10 +553,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -650,7 +656,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -685,7 +691,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -720,7 +726,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -755,7 +761,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -790,7 +796,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -825,7 +831,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -860,7 +866,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -895,7 +901,7 @@
           <t>접근 관리</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -930,7 +936,7 @@
           <t>접근 관리</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -965,7 +971,7 @@
           <t>접근 관리</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1000,7 +1006,7 @@
           <t>옵션 관리</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1035,7 +1041,7 @@
           <t>옵션 관리</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1070,7 +1076,7 @@
           <t>옵션 관리</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1105,7 +1111,7 @@
           <t>패치 관리</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1140,7 +1146,7 @@
           <t>패치 관리</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1177,7 +1183,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1212,7 +1218,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1247,7 +1253,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1280,7 +1286,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1315,7 +1321,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1352,7 +1358,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1385,7 +1391,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
@@ -1420,7 +1426,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
@@ -1455,7 +1461,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1492,7 +1498,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1525,7 +1531,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
@@ -1560,7 +1566,7 @@
           <t>계정 관리</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1597,7 +1603,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1630,7 +1636,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1667,7 +1673,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1702,7 +1708,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1737,7 +1743,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1770,7 +1776,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1807,7 +1813,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1842,7 +1848,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1877,7 +1883,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1912,7 +1918,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1945,7 +1951,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -1982,7 +1988,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2017,7 +2023,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2050,7 +2056,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2085,7 +2091,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2120,7 +2126,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2155,7 +2161,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2190,7 +2196,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2225,7 +2231,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2262,7 +2268,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>VULNERABLE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2295,7 +2301,7 @@
           <t>파일 및 디렉터리 관리</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2330,7 +2336,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2365,7 +2371,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2400,7 +2406,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2435,7 +2441,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2470,7 +2476,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2505,7 +2511,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2540,7 +2546,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2575,7 +2581,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2610,7 +2616,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2645,7 +2651,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2680,7 +2686,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2715,7 +2721,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2750,7 +2756,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2785,7 +2791,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2820,7 +2826,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2855,7 +2861,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2890,7 +2896,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2925,7 +2931,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2960,7 +2966,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -2995,7 +3001,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -3030,7 +3036,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
@@ -3065,7 +3071,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -3100,7 +3106,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
@@ -3135,7 +3141,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -3170,7 +3176,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
@@ -3205,7 +3211,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
@@ -3240,7 +3246,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
@@ -3275,7 +3281,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
@@ -3310,7 +3316,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -3345,7 +3351,7 @@
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -3380,7 +3386,7 @@
           <t>패치 관리</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -3415,7 +3421,7 @@
           <t>로그 관리</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -3450,7 +3456,7 @@
           <t>로그 관리</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -3485,7 +3491,7 @@
           <t>로그 관리</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
